--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Developer\eclipse-workspace\com.titan.eyestage\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C5C3B7-5403-4B17-9C70-CF0362AD0DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B15848-1ED5-48D7-9CDD-FA71658F4D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="4125" windowWidth="14490" windowHeight="6795" xr2:uid="{53B419D7-5DEB-49AD-9CDA-B1EC0FCC8D92}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -51,17 +49,26 @@
     <t>CLSKU</t>
   </si>
   <si>
-    <t>TW1091WHM1</t>
-  </si>
-  <si>
     <t>FrameSKU</t>
+  </si>
+  <si>
+    <t>PoweredSunglassSKU</t>
+  </si>
+  <si>
+    <t>RxP222GR1 </t>
+  </si>
+  <si>
+    <t>CBUTWD85</t>
+  </si>
+  <si>
+    <t>P449BK3TIEV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -71,9 +78,15 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
+      <color rgb="FF0F1D2A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1D2A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -96,9 +109,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,17 +426,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0575140-7AB2-45AF-BF16-5E710AC1DE63}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,23 +451,64 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B15848-1ED5-48D7-9CDD-FA71658F4D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275EB552-498E-4578-884B-4FB2F3FF12F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="6000" yWindow="4125" windowWidth="14490" windowHeight="6795" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -62,13 +65,16 @@
   </si>
   <si>
     <t>P449BK3TIEV</t>
+  </si>
+  <si>
+    <t>FT1535UFP4MGYV </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,8 +91,16 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0F1D2A"/>
-      <name val="Arial"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,10 +123,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,56 +443,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275EB552-498E-4578-884B-4FB2F3FF12F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2654C773-B54A-45C1-89F6-BD5D159530FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="4125" windowWidth="14490" windowHeight="6795" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -68,25 +65,25 @@
   </si>
   <si>
     <t>FT1535UFP4MGYV </t>
+  </si>
+  <si>
+    <t>ReadingGlassSKU</t>
+  </si>
+  <si>
+    <t>RR21 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1D2A"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -101,6 +98,18 @@
       <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1D2A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,11 +132,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,55 +452,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -502,9 +508,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -524,12 +530,21 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>6</v>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2654C773-B54A-45C1-89F6-BD5D159530FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE37E702-1329-42EB-A6DA-141735E04043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -71,26 +74,34 @@
   </si>
   <si>
     <t>RR21 </t>
+  </si>
+  <si>
+    <t>ComputerGlassSKU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT1533UFP1MBKCGV </t>
+  </si>
+  <si>
+    <t>AccessoriesSKU</t>
+  </si>
+  <si>
+    <t>SGP002WH1V</t>
+  </si>
+  <si>
+    <t>COCAWC84</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0F1D2A"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
@@ -104,6 +115,26 @@
       <color rgb="FF000000"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1D2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -132,12 +163,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,52 +490,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -507,47 +556,73 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="D3" s="7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE37E702-1329-42EB-A6DA-141735E04043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F063859-9BAF-41E2-A446-EA472D3927EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -89,6 +86,9 @@
   </si>
   <si>
     <t>COCAWC84</t>
+  </si>
+  <si>
+    <t>RxP222GR1</t>
   </si>
 </sst>
 </file>
@@ -491,20 +491,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="36.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,17 +533,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="7" t="s">
-        <v>16</v>
-      </c>
+      <c r="D2" s="7"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G2" s="5"/>
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
@@ -557,12 +557,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F063859-9BAF-41E2-A446-EA472D3927EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEB246B-D610-44C0-A2B2-F0D57D0D747E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -95,7 +98,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +142,27 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0F1D2A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -160,10 +184,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -176,8 +201,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -490,21 +519,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="36.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -533,20 +562,129 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6"/>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D16" s="8"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D17" s="9"/>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D18" s="9"/>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D19" s="10"/>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D20" s="9"/>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D21" s="10"/>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D23" s="8"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D24" s="8"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D25" s="9"/>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D26" s="10"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D27" s="9"/>
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D28" s="10"/>
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="G31" s="10"/>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I33" s="10"/>
+    </row>
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I35" s="10"/>
+    </row>
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I42" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -557,12 +695,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -620,7 +758,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEB246B-D610-44C0-A2B2-F0D57D0D747E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326881FA-69C5-44C4-905F-3F2B4029E2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -92,6 +89,18 @@
   </si>
   <si>
     <t>RxP222GR1</t>
+  </si>
+  <si>
+    <t>FT1535UFP4MGYV</t>
+  </si>
+  <si>
+    <t>OCAWC84</t>
+  </si>
+  <si>
+    <t>FT1533UFP1MBKCGV</t>
+  </si>
+  <si>
+    <t>RR21</t>
   </si>
 </sst>
 </file>
@@ -520,20 +529,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="36.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="36.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,128 +571,107 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -694,13 +682,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -729,12 +717,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
@@ -758,9 +746,84 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="D3" s="7" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326881FA-69C5-44C4-905F-3F2B4029E2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FB83F3-4348-495E-89D4-D48200646BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -529,20 +532,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="36.6640625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,107 +574,128 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -683,12 +707,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,7 +741,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -746,12 +770,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -774,7 +798,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -803,7 +827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FB83F3-4348-495E-89D4-D48200646BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51955029-F8BE-4FD8-971C-3E88FC295860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -104,13 +101,22 @@
   </si>
   <si>
     <t>RR21</t>
+  </si>
+  <si>
+    <t>Google Pay</t>
+  </si>
+  <si>
+    <t>PaymentMethod</t>
+  </si>
+  <si>
+    <t>Net Banking</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +183,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -200,7 +212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -216,6 +228,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -531,21 +544,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
-  <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="36.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,129 +586,121 @@
       <c r="I1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D2" s="7"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -706,13 +711,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -741,7 +746,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -770,12 +775,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -798,7 +803,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -827,7 +832,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -848,6 +853,16 @@
       </c>
       <c r="H11" s="6" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H15" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51955029-F8BE-4FD8-971C-3E88FC295860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156E6110-42D1-411C-BA99-31C6DC251555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -110,13 +114,22 @@
   </si>
   <si>
     <t>Net Banking</t>
+  </si>
+  <si>
+    <t>Credit / Debit Card</t>
+  </si>
+  <si>
+    <t>Cash on Delivery</t>
+  </si>
+  <si>
+    <t>Wallet</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,6 +200,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF17C6A3"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -212,7 +231,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -229,6 +248,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -545,20 +565,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,7 +610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -604,103 +624,103 @@
       <c r="G2" s="5"/>
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J2" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -711,13 +731,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -746,7 +766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -775,12 +795,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -803,7 +823,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -832,7 +852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -855,14 +875,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H15" s="11" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H16" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H18" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156E6110-42D1-411C-BA99-31C6DC251555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8744205C-2B34-4A5C-BCFA-4ACA8272CAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -565,20 +561,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,7 +606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -628,99 +624,99 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -732,12 +728,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,7 +762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -795,12 +791,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -823,7 +819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -852,7 +848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -875,27 +871,27 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" s="12" t="s">
         <v>27</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8744205C-2B34-4A5C-BCFA-4ACA8272CAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0067F93-DA82-4EC7-ADDE-0A93D673927F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="6000" yWindow="4125" windowWidth="14490" windowHeight="6795" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="28">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -561,20 +564,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -620,103 +623,139 @@
       <c r="G2" s="5"/>
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -727,13 +766,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
-  <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -791,12 +830,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -819,7 +858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -848,7 +887,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -871,29 +910,186 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H18" s="12" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>1</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="7"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>4</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0067F93-DA82-4EC7-ADDE-0A93D673927F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5E9008-BA45-42A3-BB03-709ACC99BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="4125" windowWidth="14490" windowHeight="6795" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="28">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -564,20 +561,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -623,139 +620,210 @@
       <c r="G2" s="5"/>
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
-      <c r="J2" t="s">
+      <c r="J2" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="5"/>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -767,12 +835,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +869,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -830,12 +898,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -858,7 +926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -869,7 +937,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>18</v>
@@ -887,7 +955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -910,32 +978,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -967,7 +1035,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -985,7 +1053,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2</v>
       </c>
@@ -996,7 +1064,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1028,7 +1096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1060,7 +1128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>5</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5E9008-BA45-42A3-BB03-709ACC99BA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5F0675-A488-4264-85C2-F750C112CAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="30">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -119,6 +120,12 @@
   </si>
   <si>
     <t>Wallet</t>
+  </si>
+  <si>
+    <t>LoginUser</t>
+  </si>
+  <si>
+    <t>DEFAULT_USER</t>
   </si>
 </sst>
 </file>
@@ -560,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -572,9 +579,10 @@
     <col min="7" max="7" width="15.109375" customWidth="1"/>
     <col min="8" max="8" width="23.6640625" customWidth="1"/>
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,12 +613,17 @@
       <c r="J1" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
@@ -623,8 +636,11 @@
       <c r="J2" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -634,8 +650,11 @@
       <c r="J3" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -666,8 +685,11 @@
       <c r="J4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -698,8 +720,11 @@
       <c r="J5" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -730,14 +755,17 @@
       <c r="J6" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
@@ -1163,4 +1191,171 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D340067D-92C5-4A87-863D-4C9C26FE9C40}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5F0675-A488-4264-85C2-F750C112CAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66977AC-FDEA-4804-BDBD-F548F0F36333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="30">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -568,21 +571,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,13 +620,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
@@ -640,7 +641,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -654,7 +655,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -689,7 +690,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -724,7 +725,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -759,99 +760,99 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -863,12 +864,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -897,7 +898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -926,12 +927,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -954,7 +955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -983,7 +984,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1006,32 +1007,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1064,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -1081,7 +1082,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -1092,7 +1093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1124,7 +1125,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1156,7 +1157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -1196,9 +1197,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D340067D-92C5-4A87-863D-4C9C26FE9C40}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1230,7 +1231,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1248,7 +1249,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1259,7 +1260,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1291,7 +1292,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66977AC-FDEA-4804-BDBD-F548F0F36333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F85C23C-2D11-42FD-AF02-431D72C79965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
@@ -642,123 +642,40 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
+      <c r="C3" s="5"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
@@ -1196,10 +1113,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D340067D-92C5-4A87-863D-4C9C26FE9C40}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1231,7 +1148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1249,7 +1166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1260,7 +1177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1292,7 +1209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1324,7 +1241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1354,6 +1271,125 @@
       </c>
       <c r="J6" s="12" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F85C23C-2D11-42FD-AF02-431D72C79965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E31C17E-A22F-4A12-933D-69E05ADA7199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="30">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -571,21 +568,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.6640625" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -620,7 +617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -641,135 +638,218 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="5"/>
-      <c r="J3" s="12"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -781,12 +861,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="32.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,7 +895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -844,12 +924,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -872,7 +952,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -901,7 +981,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -924,32 +1004,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
       <c r="H18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +1061,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -999,7 +1079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>2</v>
       </c>
@@ -1010,7 +1090,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1042,7 +1122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1074,7 +1154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>5</v>
       </c>
@@ -1114,9 +1194,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D340067D-92C5-4A87-863D-4C9C26FE9C40}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,7 +1228,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1166,7 +1246,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1177,7 +1257,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1209,7 +1289,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1241,7 +1321,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1273,7 +1353,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1287,7 +1367,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1322,7 +1402,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1357,7 +1437,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>5</v>
       </c>

--- a/TestData/AddToCart.xlsx
+++ b/TestData/AddToCart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E31C17E-A22F-4A12-933D-69E05ADA7199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9600A1D-2DF5-41A4-B9FC-E8E6F73536CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="30">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -568,21 +571,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
   <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -631,225 +634,142 @@
       <c r="G2" s="5"/>
       <c r="H2" s="4"/>
       <c r="I2" s="6"/>
-      <c r="J2" s="12" t="s">
-        <v>27</v>
+      <c r="J2" t="s">
+        <v>22</v>
       </c>
       <c r="K2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="J3" s="12"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="11"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="12"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16" s="8"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D17" s="9"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="9"/>
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D20" s="9"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D21" s="10"/>
     </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D23" s="8"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D24" s="8"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D28" s="10"/>
     </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
       <c r="G31" s="10"/>
       <c r="I31" s="9"/>
     </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I34" s="9"/>
     </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I35" s="10"/>
     </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I40" s="9"/>
     </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I41" s="9"/>
     </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I42" s="10"/>
     </row>
   </sheetData>
@@ -861,12 +781,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -924,12 +844,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -952,7 +872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -981,7 +901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1004,32 +924,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +981,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -1079,7 +999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -1090,7 +1010,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1122,7 +1042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1154,7 +1074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -1194,9 +1114,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D340067D-92C5-4A87-863D-4C9C26FE9C40}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1246,7 +1166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1257,7 +1177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1289,7 +1209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1321,7 +1241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1353,7 +1273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1367,7 +1287,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1402,7 +1322,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1437,7 +1357,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
